--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129584754</v>
       </c>
       <c r="B3" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129584390</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129585387</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129585212</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,44 +776,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129584754</v>
+        <v>129585387</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -822,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517314</v>
+        <v>517346</v>
       </c>
       <c r="R3" t="n">
-        <v>6705182</v>
+        <v>6705238</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,33 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129584390</v>
+        <v>129584754</v>
       </c>
       <c r="B4" t="n">
-        <v>91625</v>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -927,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517370</v>
+        <v>517314</v>
       </c>
       <c r="R4" t="n">
-        <v>6705191</v>
+        <v>6705182</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,11 +959,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En döende fruktkropp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,107 +983,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>129585387</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91605</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>V Bjusmyran, Dlr</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>517346</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6705238</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24594-2025 artfynd.xlsx
+++ b/artfynd/A 24594-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129585212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129585387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129584754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>